--- a/data/cv_master.xlsx
+++ b/data/cv_master.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="600" firstSheet="0" activeTab="8" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30240" yWindow="-1460" windowWidth="38400" windowHeight="21100" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_README" sheetId="1" state="visible" r:id="rId1"/>
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -54,13 +54,6 @@
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
       <family val="3"/>
-      <sz val="6"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="128"/>
-      <family val="2"/>
       <sz val="6"/>
       <scheme val="minor"/>
     </font>
@@ -95,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -108,6 +101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -707,23 +701,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="3"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="7"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="12"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="10" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="15"/>
+    <col width="12" customWidth="1" min="13" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -780,21 +766,6 @@
       <c r="K1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
         </is>
       </c>
     </row>
@@ -809,26 +780,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="10"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="12"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="15"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="13" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="18"/>
+    <col width="12" customWidth="1" min="16" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,72 +809,52 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>committee_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>committee_ja</t>
+          <t>committee_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>committee_en</t>
+          <t>organization_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>organization_ja</t>
+          <t>organization_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>organization_en</t>
+          <t>role_ja</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>role_ja</t>
+          <t>role_en</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>role_en</t>
+          <t>committee_type</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>committee_type</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
           <t>visible_cv_short</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
         </is>
       </c>
     </row>
@@ -929,26 +869,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="4"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="10"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="15"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="13" max="14"/>
     <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="18"/>
+    <col width="12" customWidth="1" min="16" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1020,21 +951,6 @@
       <c r="N1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
         </is>
       </c>
     </row>
@@ -1049,23 +965,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="8"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="12"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="10" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="15"/>
+    <col width="12" customWidth="1" min="13" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1086,57 +994,37 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>organization_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>organization_ja</t>
+          <t>organization_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>organization_en</t>
+          <t>membership_type_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>membership_type_ja</t>
+          <t>membership_type_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>membership_type_en</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
           <t>visible_cv_short</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
         </is>
       </c>
     </row>
@@ -1152,39 +1040,23 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>米国人類遺伝学会</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>米国人類遺伝学会</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
           <t>American Society of Human Genetics</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
         <v>0</v>
       </c>
       <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Join year from ORCID. Not shown on the website.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>researchmap;orcid</t>
-        </is>
-      </c>
-      <c r="N2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1200,39 +1072,23 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>日本人類遺伝学会</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>日本人類遺伝学会</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
           <t>Japanese Society of Human Genetics</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="b">
         <v>0</v>
       </c>
       <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Join year from ORCID. Not shown on the website.</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>researchmap;orcid</t>
-        </is>
-      </c>
-      <c r="N3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1248,39 +1104,23 @@
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>日本バイオインフォマティクス学会</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>日本バイオインフォマティクス学会</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>Japanese Society for Bioinformatics</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="b">
         <v>0</v>
       </c>
       <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Join year from ORCID. Not shown on the website.</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>researchmap;orcid</t>
-        </is>
-      </c>
-      <c r="N4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1296,39 +1136,23 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>日本癌学会</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>日本癌学会</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>Japanese Cancer Association</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Join year from ORCID. Not shown on the website.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>researchmap;orcid</t>
-        </is>
-      </c>
-      <c r="N5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1343,25 +1167,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="12"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="14"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="17"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="34" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="20"/>
   </cols>
@@ -1384,65 +1196,60 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>position_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>position_ja</t>
+          <t>position_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>position_en</t>
+          <t>department_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>department_ja</t>
+          <t>department_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>department_en</t>
+          <t>institution_ja</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>institution_ja</t>
+          <t>institution_en</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>institution_en</t>
+          <t>location_ja</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>location_ja</t>
+          <t>location_en</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>location_en</t>
+          <t>appointment_type</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>appointment_type</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -1460,61 +1267,58 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>助教</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>助教</t>
+          <t>Assistant Professor</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Assistant Professor</t>
+          <t>大学院医学系研究科 遺伝情報学</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>大学院医学系研究科 遺伝情報学</t>
+          <t>Department of Genome Informatics, Graduate School of Medicine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Department of Genome Informatics, Graduate School of Medicine</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>東京大学</t>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>The University of Tokyo</t>
+          <t>東京, 日本</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>東京, 日本</t>
+          <t>Tokyo, Japan</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Tokyo, Japan</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
           <t>primary</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1530,61 +1334,58 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>客員研究員</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>客員研究員</t>
+          <t>Invited Faculty</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Invited Faculty</t>
+          <t>システム遺伝学研究チーム</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>システム遺伝学研究チーム</t>
+          <t>Laboratory for Systems Genetics</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Laboratory for Systems Genetics</t>
+          <t>理化学研究所 生命医科学研究センター</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>理化学研究所 生命医科学研究センター</t>
+          <t>RIKEN Center for Integrative Medical Sciences</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>RIKEN Center for Integrative Medical Sciences</t>
+          <t>横浜, 日本</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>横浜, 日本</t>
+          <t>Yokohama, Japan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Yokohama, Japan</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
           <t>invited</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="b">
         <v>1</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1604,61 +1405,58 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D4" t="b">
-        <v>0</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>招へい教員</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>招へい教員</t>
+          <t>Invited Faculty</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Invited Faculty</t>
+          <t>大学院医学系研究科 遺伝統計学</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>大学院医学系研究科 遺伝統計学</t>
+          <t>Department of Statistical Genetics, Graduate School of Medicine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Department of Statistical Genetics, Graduate School of Medicine</t>
+          <t>大阪大学</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>大阪大学</t>
+          <t>The University of Osaka</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>The University of Osaka</t>
+          <t>大阪, 日本</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>大阪, 日本</t>
+          <t>Osaka, Japan</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Osaka, Japan</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
           <t>invited</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="M4" t="n">
         <v>2</v>
       </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
       <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1673,24 +1471,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="12"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="16"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="34" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="19"/>
   </cols>
@@ -1713,60 +1500,55 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>position_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>position_ja</t>
+          <t>position_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>position_en</t>
+          <t>institution_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>institution_ja</t>
+          <t>institution_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>institution_en</t>
+          <t>department_ja</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>department_ja</t>
+          <t>department_en</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>department_en</t>
+          <t>location_ja</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>location_ja</t>
+          <t>location_en</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>location_en</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -1788,46 +1570,43 @@
           <t>2020-03</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>初期研修医</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>初期研修医</t>
+          <t>Junior Resident</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Junior Resident</t>
+          <t>日本赤十字社医療センター</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>日本赤十字社医療センター</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Japan Red Cross Medical Center</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>東京, 日本</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>東京, 日本</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="b">
+        <v>1</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1842,28 +1621,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="16"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
-    <col width="34" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="17" customWidth="1" min="18" max="20"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="23"/>
   </cols>
@@ -1886,80 +1650,75 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>degree_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>degree_ja</t>
+          <t>degree_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>degree_en</t>
+          <t>field_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>field_ja</t>
+          <t>field_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>field_en</t>
+          <t>department_ja</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>department_ja</t>
+          <t>department_en</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>department_en</t>
+          <t>institution_ja</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>institution_ja</t>
+          <t>institution_en</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>institution_en</t>
+          <t>advisor_ja</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>advisor_ja</t>
+          <t>advisor_en</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>advisor_en</t>
+          <t>location_ja</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>location_ja</t>
+          <t>location_en</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t>location_en</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -1981,76 +1740,73 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>博士（医学）</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>博士（医学）</t>
+          <t>Ph.D. (Medicine)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ph.D. (Medicine)</t>
+          <t>遺伝統計学</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>遺伝統計学</t>
+          <t>Department of Statistical Genetics</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Statistical Genetics</t>
+          <t>大学院医学系研究科 医学専攻</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>大学院医学系研究科 医学専攻</t>
+          <t>Graduate School of Medicine</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Division of Medicine, Graduate School of Medicine</t>
+          <t>大阪大学</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>大阪大学</t>
+          <t>The University of Osaka</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>The University of Osaka</t>
+          <t>岡田 随象</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>岡田 随象</t>
+          <t>Yukinori Okada</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Yukinori Okada</t>
+          <t>大阪, 日本</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>大阪, 日本</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
           <t>Osaka, Japan</t>
         </is>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
       </c>
       <c r="R2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2070,51 +1826,48 @@
           <t>2018-03</t>
         </is>
       </c>
-      <c r="D3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>M.D.</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>医学部医学科</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>医学部医学科</t>
+          <t>Faculty of Medicine</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>School of Medicine, Faculty of Medicine</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>東京大学</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
           <t>The University of Tokyo</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>東京, 日本</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>東京, 日本</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
           <t>Tokyo, Japan</t>
         </is>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
       </c>
       <c r="R3" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2130,20 +1883,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="8"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="12"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="15"/>
   </cols>
@@ -2369,8 +2115,48 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ashg_reviewers_choice_2020</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>44131</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Reviewer's Choice Abstract</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Reviewer's Choice Abstract</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>アメリカ人類遺伝学会2020年会</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>American Society of Human Genetics Annual Meeting 2020</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -2380,26 +2166,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="8"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="12"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="17" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="14"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="18"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
     <col width="34" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="21"/>
   </cols>
@@ -2422,70 +2198,65 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>fellowship_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>fellowship_ja</t>
+          <t>fellowship_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>fellowship_en</t>
+          <t>organization_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>organization_ja</t>
+          <t>organization_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>organization_en</t>
+          <t>amount_jpy</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>amount_jpy</t>
+          <t>show_amount_web</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_web</t>
+          <t>show_amount_cv_short</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_cv_short</t>
+          <t>show_amount_cv_full</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_cv_full</t>
+          <t>description_ja</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>description_ja</t>
+          <t>description_en</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>description_en</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -2507,48 +2278,45 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>0</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>医学部博士課程奨学助成</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医学部博士課程奨学助成</t>
+          <t>Scholarship Grant for Ph.D. Program in Medicine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Scholarship Grant for Ph.D. Program in Medicine</t>
+          <t>武田科学振興財団</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>武田科学振興財団</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>Takeda Science Foundation</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>14400000</v>
       </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
       </c>
-      <c r="L2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
       </c>
       <c r="P2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2563,33 +2331,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" style="4" min="2" max="3"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" style="4" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="4"/>
     <col width="34" customWidth="1" min="5" max="10"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="12"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="15"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="19"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="17" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="34" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="17" customWidth="1" min="23" max="25"/>
-    <col width="17" customWidth="1" min="24" max="24"/>
     <col width="34" customWidth="1" min="26" max="26"/>
     <col width="12" customWidth="1" min="27" max="28"/>
   </cols>
@@ -2612,105 +2368,100 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>agency_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>agency_ja</t>
+          <t>agency_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>agency_en</t>
+          <t>program_ja</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>program_ja</t>
+          <t>program_en</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>program_en</t>
+          <t>title_ja</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>title_ja</t>
+          <t>title_en</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>title_en</t>
+          <t>role</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>grant_number</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>grant_number</t>
+          <t>show_grant_number_web</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>show_grant_number_web</t>
+          <t>show_grant_number_cv_short</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>show_grant_number_cv_short</t>
+          <t>show_grant_number_cv_full</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>show_grant_number_cv_full</t>
+          <t>amount_jpy</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t>amount_jpy</t>
+          <t>show_amount_web</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_web</t>
+          <t>show_amount_cv_short</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_cv_short</t>
+          <t>show_amount_cv_full</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>show_amount_cv_full</t>
+          <t>amount_type</t>
         </is>
       </c>
       <c r="T1" s="2" t="inlineStr">
         <is>
-          <t>amount_type</t>
+          <t>url</t>
         </is>
       </c>
       <c r="U1" s="2" t="inlineStr">
         <is>
-          <t>url</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="V1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="W1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -2732,87 +2483,84 @@
           <t>2028-03</t>
         </is>
       </c>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>日本学術振興会</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>日本学術振興会</t>
+          <t>Japan Society for the Promotion of Science (JSPS)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Japan Society for the Promotion of Science (JSPS)</t>
+          <t>科学研究費助成事業 若手研究</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>科学研究費助成事業 若手研究</t>
+          <t>Grant-in-Aid for Early-Career Scientists</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Grant-in-Aid for Early-Career Scientists</t>
+          <t>深層学習によるヒト脂質代謝の遺伝的基盤全体像の解明</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>深層学習によるヒト脂質代謝の遺伝的基盤全体像の解明</t>
+          <t>Deep learning-based elucidation of the genetic architecture of human lipid metabolism</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deep learning-based elucidation of the genetic architecture of human lipid metabolism</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
           <t>26K18279</t>
         </is>
       </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
       <c r="M2" t="b">
         <v>0</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="O2" t="n">
         <v>3500000</v>
       </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
       <c r="R2" t="b">
         <v>0</v>
       </c>
-      <c r="S2" t="b">
-        <v>0</v>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>total_project</t>
+        </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>total_project</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
           <t>https://kaken.nii.ac.jp/grant/KAKENHI-PROJECT-26K18279</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="b">
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
-      </c>
-      <c r="X2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2832,82 +2580,79 @@
           <t>2028-03</t>
         </is>
       </c>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>ゲノム創薬基盤推進研究事業</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ゲノム創薬基盤推進研究事業</t>
+          <t>Genome-based Drug Discovery Program</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Genome-based Drug Discovery Program</t>
+          <t>遺伝子変異の機能性スペクトラム統一的解析と次世代創薬連携による創薬シーズ導出</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>遺伝子変異の機能性スペクトラム統一的解析と次世代創薬連携による創薬シーズ導出</t>
+          <t>Establishment of drug candidates through integrative analysis of the functional spectrum of genetic mutations and interdisciplinary collaboration of next-generation drug discovery fields</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Establishment of drug candidates through integrative analysis of the functional spectrum of genetic mutations and interdisciplinary collaboration of next-generation drug discovery fields</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>JP25kk0305032</t>
         </is>
       </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
       <c r="M3" t="b">
         <v>0</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="b">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="O3" t="n">
         <v>66000000</v>
       </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3" t="b">
         <v>0</v>
       </c>
-      <c r="S3" t="b">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
-      </c>
-      <c r="X3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2927,82 +2672,79 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>ゲノム医療実現推進プラットフォーム・先端ゲノム研究開発 (GRIFIN)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ゲノム医療実現推進プラットフォーム・先端ゲノム研究開発 (GRIFIN)</t>
+          <t>Advanced Genome Research and Bioinformatics Study to Facilitate Medical Innovation</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Advanced Genome Research and Bioinformatics Study to Facilitate Medical Innovation</t>
+          <t>遺伝子–環境相互作用の学術・オミクス横断による個別化医療の実装</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>遺伝子–環境相互作用の学術・オミクス横断による個別化医療の実装</t>
+          <t>A trans-disciplinary and trans-omics study of gene–environment interactions towards genomics-driven personalized medicine</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A trans-disciplinary and trans-omics study of gene–environment interactions towards genomics-driven personalized medicine</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>JP24tm0424228</t>
         </is>
       </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
       <c r="M4" t="b">
         <v>0</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="O4" t="n">
         <v>22800000</v>
       </c>
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4" t="b">
         <v>0</v>
       </c>
-      <c r="S4" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
-      </c>
-      <c r="X4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3018,77 +2760,74 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>日本応用酵素協会</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>日本応用酵素協会</t>
+          <t>Japan Foundation for Applied Enzymology</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Japan Foundation for Applied Enzymology</t>
+          <t>Cardiovascular Innovative Conference に関する研究助成 (CVIC)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cardiovascular Innovative Conference に関する研究助成 (CVIC)</t>
+          <t>Grants related to Cardiovascular Innovative Conference</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Grants related to Cardiovascular Innovative Conference</t>
+          <t>心血管疾患の遺伝子–環境相互作用解明によるゲノム個別化医療と創薬</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>心血管疾患の遺伝子–環境相互作用解明によるゲノム個別化医療と創薬</t>
+          <t>Genomics-driven personalized medicine and drug discovery by elucidating gene–environment interactions for cardiovascular diseases</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Genomics-driven personalized medicine and drug discovery by elucidating gene–environment interactions for cardiovascular diseases</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>PI</t>
         </is>
       </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
       <c r="M5" t="b">
         <v>0</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="O5" t="n">
         <v>950000</v>
       </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5" t="b">
         <v>0</v>
       </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
-      </c>
-      <c r="X5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3108,83 +2847,80 @@
           <t>2028-03</t>
         </is>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>医学系研究支援プログラム</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>医学系研究支援プログラム</t>
+          <t>Medical Research Support Program</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Medical Research Support Program</t>
+          <t>心代謝性疾患のゲノム解析・オミクス統合による疾患病態解明</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>心代謝性疾患のゲノム解析・オミクス統合による疾患病態解明</t>
+          <t>Elucidating the pathophysiology of cardiometabolic diseases through genetic analyses and omics integration</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Elucidating the pathophysiology of cardiometabolic diseases through genetic analyses and omics integration</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>JP256f0137004</t>
         </is>
       </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
       <c r="M6" t="b">
         <v>0</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="O6" t="n">
         <v>41250000</v>
       </c>
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6" t="b">
         <v>0</v>
       </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
       </c>
       <c r="W6" t="b">
         <v>1</v>
-      </c>
-      <c r="X6" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3203,83 +2939,80 @@
           <t>2028-03</t>
         </is>
       </c>
-      <c r="D7" t="b">
-        <v>1</v>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>難治性疾患実用化研究事業</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>難治性疾患実用化研究事業</t>
+          <t>Practical Research Project for Rare/Intractable Diseases</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Practical Research Project for Rare/Intractable Diseases</t>
+          <t>オールジャパン心筋症ゲノムオミックスデジタルコホート研究（代表: 野村征太郎）</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>オールジャパン心筋症ゲノムオミックスデジタルコホート研究（代表: 野村征太郎）</t>
+          <t>All-Japan Cardiomyopathy Genome Omics Digital Cohort Study</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>All-Japan Cardiomyopathy Genome Omics Digital Cohort Study</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>co-investigator</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>JP25ek0109795h0001</t>
         </is>
       </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
       <c r="M7" t="b">
         <v>0</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="O7" t="n">
         <v>1500000</v>
       </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7" t="b">
         <v>0</v>
       </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
       </c>
       <c r="W7" t="b">
         <v>1</v>
-      </c>
-      <c r="X7" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3298,83 +3031,80 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>ゲノム研究を創薬等出口に繋げる研究開発プログラム</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ゲノム研究を創薬等出口に繋げる研究開発プログラム</t>
+          <t>Research and Development Program for Bridging Genomic Research to Drug Discovery and Other Outcomes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Research and Development Program for Bridging Genomic Research to Drug Discovery and Other Outcomes</t>
+          <t>デジタロミクスによる心不全ストレス応答の機序解明と精密医療（代表: 野村征太郎）</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>デジタロミクスによる心不全ストレス応答の機序解明と精密医療（代表: 野村征太郎）</t>
+          <t>Digital omics to elucidate mechanisms of stress responses in heart failure for precision medicine</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Digital omics to elucidate mechanisms of stress responses in heart failure for precision medicine</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
           <t>co-investigator</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>JP24tm0524009</t>
         </is>
       </c>
+      <c r="L8" t="b">
+        <v>0</v>
+      </c>
       <c r="M8" t="b">
         <v>0</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="b">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="O8" t="n">
         <v>9000000</v>
       </c>
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8" t="b">
         <v>0</v>
       </c>
-      <c r="S8" t="b">
-        <v>0</v>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>0</v>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
       </c>
       <c r="W8" t="b">
         <v>1</v>
-      </c>
-      <c r="X8" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -3393,83 +3123,80 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D9" t="b">
-        <v>0</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>日本医療研究開発機構（AMED）</t>
+        </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>日本医療研究開発機構（AMED）</t>
+          <t>Japan Agency for Medical Research and Development (AMED)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Japan Agency for Medical Research and Development (AMED)</t>
+          <t>ゲノム研究を創薬等出口に繋げる研究開発プログラム</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ゲノム研究を創薬等出口に繋げる研究開発プログラム</t>
+          <t>Research and Development Program for Bridging Genomic Research to Drug Discovery and Other Outcomes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Research and Development Program for Bridging Genomic Research to Drug Discovery and Other Outcomes</t>
+          <t>脳血管のゲノム解析と血流解析の統合による脳血管障害発症に至る軌跡の解明と診療応用を目指す研究（代表: 鎌谷洋一郎）</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>脳血管のゲノム解析と血流解析の統合による脳血管障害発症に至る軌跡の解明と診療応用を目指す研究（代表: 鎌谷洋一郎）</t>
+          <t>Elucidating the Trajectory of Cerebrovascular Disorders through Integrated Genomic Analysis and Hemodynamic Simulation for Clinical Applications</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Elucidating the Trajectory of Cerebrovascular Disorders through Integrated Genomic Analysis and Hemodynamic Simulation for Clinical Applications</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
           <t>co-investigator</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>JP24tm0524003</t>
         </is>
       </c>
+      <c r="L9" t="b">
+        <v>0</v>
+      </c>
       <c r="M9" t="b">
         <v>0</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="b">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="O9" t="n">
         <v>3000000</v>
       </c>
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
       <c r="R9" t="b">
         <v>0</v>
       </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="b">
+        <v>1</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
-      </c>
-      <c r="X9" t="b">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -3488,83 +3215,80 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D10" t="b">
-        <v>1</v>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>東京大学新世代感染症センター (UTOPIA)</t>
+        </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>東京大学新世代感染症センター (UTOPIA)</t>
+          <t>The University of Tokyo Pandemic Preparedness, Infection, and Advanced Research Center (UTOPIA)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The University of Tokyo Pandemic Preparedness, Infection, and Advanced Research Center (UTOPIA)</t>
+          <t>若手研究プログラム</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>若手研究プログラム</t>
+          <t>Grant in Aid for Young Scientists</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Grant in Aid for Young Scientists</t>
+          <t>感染症の重症化・遷延化を標的とするゲノム創薬の実装</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>感染症の重症化・遷延化を標的とするゲノム創薬の実装</t>
+          <t>Implementation of genome-based drug discovery targeting severe and prolonged infectious diseases</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Implementation of genome-based drug discovery targeting severe and prolonged infectious diseases</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>JP223fa627001</t>
         </is>
       </c>
+      <c r="L10" t="b">
+        <v>0</v>
+      </c>
       <c r="M10" t="b">
         <v>0</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="b">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="O10" t="n">
         <v>5000000</v>
       </c>
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
       <c r="R10" t="b">
         <v>0</v>
       </c>
-      <c r="S10" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>total_project</t>
         </is>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="b">
+        <v>1</v>
       </c>
       <c r="W10" t="b">
         <v>1</v>
-      </c>
-      <c r="X10" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3579,25 +3303,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="4"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="6"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="13"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="17" customWidth="1" min="15" max="17"/>
-    <col width="17" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3618,65 +3332,60 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>course_ja</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>course_ja</t>
+          <t>course_en</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>course_en</t>
+          <t>activity_type</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>activity_type</t>
+          <t>institution_ja</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>institution_ja</t>
+          <t>institution_en</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>institution_en</t>
+          <t>school_ja</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>school_ja</t>
+          <t>school_en</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>school_en</t>
+          <t>role_ja</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>role_ja</t>
+          <t>role_en</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>role_en</t>
+          <t>sort_order</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>sort_order</t>
+          <t>visible_web</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>visible_web</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
@@ -3694,51 +3403,48 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" t="b">
-        <v>1</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>医学に接する</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>医学に接する</t>
+          <t>Introduction to Medicine</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Introduction to Medicine Seminar</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>seminar</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>東京大学</t>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>The University of Tokyo</t>
+          <t>医学部</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>医学部</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>Faculty of Medicine</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3754,51 +3460,48 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" t="b">
-        <v>1</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>生化学講義</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>生化学講義</t>
+          <t>Biochemistry (Lecture)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biochemistry (Lecture)</t>
+          <t>lecture</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>lecture</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>東京大学</t>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The University of Tokyo</t>
+          <t>医学部</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>医学部</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>Faculty of Medicine</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3814,51 +3517,48 @@
         </is>
       </c>
       <c r="C4" s="4" t="n"/>
-      <c r="D4" t="b">
-        <v>1</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>遺伝情報学各論</t>
+        </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>遺伝情報学各論</t>
+          <t>Advanced Genome Informatics</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Advanced Genetic Informatics</t>
+          <t>lecture</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>lecture</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>東京大学</t>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The University of Tokyo</t>
+          <t>大学院医学系研究科</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>大学院医学系研究科</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>Graduate School of Medicine</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
-      </c>
-      <c r="P4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3874,51 +3574,48 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" t="b">
-        <v>1</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>生化学実習</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>生化学実習</t>
+          <t>Biochemistry (Laboratory Course)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Biochemistry (Laboratory Course)</t>
+          <t>laboratory</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>laboratory</t>
+          <t>東京大学</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>東京大学</t>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>The University of Tokyo</t>
+          <t>医学部</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>医学部</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>Faculty of Medicine</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3938,42 +3635,44 @@
           <t>2023-09</t>
         </is>
       </c>
-      <c r="D6" t="b">
-        <v>0</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>臨床遺伝学</t>
+        </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>臨床遺伝学</t>
+          <t>Clinical Genetics</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Clinical Genetics</t>
+          <t>teaching assistant</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>teaching assistant</t>
+          <t>大阪大学</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>大阪大学</t>
+          <t>The University of Osaka</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The University of Osaka</t>
+          <t>医学部</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>医学部</t>
+          <t>Faculty of Medicine</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Faculty of Medicine</t>
+          <t>Teaching Assistant</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -3981,18 +3680,13 @@
           <t>Teaching Assistant</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Teaching Assistant</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
-      </c>
-      <c r="P6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4008,27 +3702,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="10"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="16"/>
-    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="14" max="15"/>
     <col width="34" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="19"/>
+    <col width="12" customWidth="1" min="17" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4087,43 +3771,740 @@
           <t>talk_type</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
+          <t>symposium session</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
           <t>sort_order</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>visible_web</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>visible_cv_short</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="R1" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023_jshg</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>45211</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Polygenic germline effects on cancer somatic alterations</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Polygenic germline effects on cancer somatic alterations</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>日本人類遺伝学会第68回大会</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Japanese Society of Human Genetics 2023</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>日本人類遺伝学会</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Japanese Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Cancer Genomics [somatic]</t>
+        </is>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024_jshg</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>45577</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>生殖細胞・体細胞変異・遺伝-環境相互作用の統合解析</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Integrative analyses of germline variants, somatic mutations, and gene–environment interactions</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>日本人類遺伝学会第69回大会</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Japanese Society of Human Genetics 2024</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>日本人類遺伝学会</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Japanese Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>多因子疾患とポリジェニック・リスク・スコアの実装に向けて</t>
+        </is>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024_wcpg</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>45582</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Genome and omics data with rich disease phenotypes in BioBank Japan provide insights into disease biology and personalized medicine</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Genome and omics data with rich disease phenotypes in BioBank Japan provide insights into disease biology and personalized medicine</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics 2024</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics 2024</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>International Society of Psychiatric Genetics</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>International Society of Psychiatric Genetics</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>シンガポール</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Longitudinal Genetic Approaches in Mental Health: International Perspectives and Opportunities</t>
+        </is>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025_agw</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>45840</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gene–environment interactions underlying the dynamics of genetic architecture</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Gene–environment interactions underlying the dynamics of genetic architecture</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>第15回国際ゲノム会議</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The 15th International Workshop on Advanced Genomics</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>第15回国際ゲノム会議</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>The 15th International Workshop on Advanced Genomics</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Large-scale Genome</t>
+        </is>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025_pabc</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>45966</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Cross-biobank studies</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Cross-biobank studies</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025 East Asia Biobank Symposium</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2025 East Asia Biobank Symposium</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Department of Biostatistics and Department of Epidemiology, Harvard T.H. Chan School of Public Health</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Department of Biostatistics and Department of Epidemiology, Harvard T.H. Chan School of Public Health</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Session-4</t>
+        </is>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025_f2f</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>45903</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Biobank Japan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Biobank Japan</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>FinnGen Face-to-Face Helsinki 2025</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>FinnGen Face-to-Face Helsinki 2025</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>FinnGen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>フィンランド</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Finnland</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>New analyses and global collaboration</t>
+        </is>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026_scarda</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>46051</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>複数人種集団における遺伝子–環境交互作用アトラスは遺伝的構造の動的な変動を明らかにする</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Gene–environment interactions underlying the dynamics of genetic architecture</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SCARDA 第6回 京都大学・理化学研究所・東京大学サポート機関合同シンポジウム</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The 6th SCARDA Joint Symposium of the Support Institutions at Kyoto University, RIKEN, and the University of Tokyo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>理化学研究所</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>RIKEN</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>symposium</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Session-1</t>
+        </is>
+      </c>
+      <c r="O8" t="b">
+        <v>1</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026_utnep</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>46035</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ヒト疾患形質の遺伝的構造の動的な変動の解明</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gene–environment interactions underlying the dynamics of genetic architecture</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>東京大学腎臓内科</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Department of Nephrology, The University of Tokyo Hospital</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>東京大学腎臓内科</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Department of Nephrology, The University of Tokyo Hospital</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>日本</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>seminar</t>
+        </is>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026_utdm</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>46070</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ヒト疾患形質の遺伝的構造の動的な変動の解明</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gene–environment interactions underlying the dynamics of genetic architecture</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>東京大学糖尿病代謝内科</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Department of Diabetes and Metabolic Diseases, The University of Tokyo Hospital</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>東京大学糖尿病代謝内科</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Department of Diabetes and Metabolic Diseases, The University of Tokyo Hospital</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>日本（オンライン）</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Japan (virtual)</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>seminar</t>
+        </is>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2023_manning</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>45279</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A cross-population atlas of genome-wide gene-environment interactions between the East Asian and European populations</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A cross-population atlas of genome-wide gene-environment interactions between the East Asian and European populations</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Prof. Alisa Manning Lab, Massachusetts General Hospital and Broad Institute</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Prof. Alisa Manning Lab, Massachusetts General Hospital and Broad Institute</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Prof. Alisa Manning Lab, Massachusetts General Hospital and Broad Institute</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Prof. Alisa Manning Lab, Massachusetts General Hospital and Broad Institute</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>アメリカ（オンライン）</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>US (virtual)</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>seminar</t>
+        </is>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026_pgccp</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A Cross-population Compendium of Gene–Environment Interactions</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A Cross-population Compendium of Gene–Environment Interactions</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Consortium Cross-population Working Group</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Consortium Cross-population Working Group</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Consortium Cross-population Working Group</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Consortium Cross-population Working Group</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>オンライン</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>seminar</t>
+        </is>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/cv_master.xlsx
+++ b/data/cv_master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nanbashinichi/Dropbox/shinichinamba/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C392403B-46C2-DA42-B7CA-0031F325DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B64749-DADB-554E-8644-F3A7183A1979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12800" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54860" yWindow="3240" windowWidth="38400" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_README" sheetId="1" r:id="rId1"/>
@@ -136,9 +136,6 @@
     <t>ashg_reviewers_choice_2020</t>
   </si>
   <si>
-    <t>Reviewer's Choice Abstract</t>
-  </si>
-  <si>
     <t>アメリカ人類遺伝学会2020年会</t>
   </si>
   <si>
@@ -1139,25 +1136,6 @@
   </si>
   <si>
     <t>Japanese Cancer Association</t>
-  </si>
-  <si>
-    <t>Cardiovascular Innovative Conferernce第4回研究発表会優秀賞</t>
-    <rPh sb="37" eb="38">
-      <t xml:space="preserve">ダイ4 </t>
-    </rPh>
-    <rPh sb="39" eb="40">
-      <t xml:space="preserve">カイ </t>
-    </rPh>
-    <rPh sb="40" eb="45">
-      <t xml:space="preserve">ケンキュウハッピョウカイ </t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t xml:space="preserve">ユウシュウシャ </t>
-    </rPh>
-    <rPh sb="47" eb="48">
-      <t xml:space="preserve">ショウ </t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>日本応用酵素協会</t>
@@ -1176,6 +1154,29 @@
   </si>
   <si>
     <t>cvic_2026</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Reviewer's Choice Abstract Award</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>Cardiovascular Innovative Conference第4回研究発表会優秀賞</t>
+    <rPh sb="36" eb="37">
+      <t xml:space="preserve">ダイ4 </t>
+    </rPh>
+    <rPh sb="38" eb="39">
+      <t xml:space="preserve">カイ </t>
+    </rPh>
+    <rPh sb="39" eb="44">
+      <t xml:space="preserve">ケンキュウハッピョウカイ </t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t xml:space="preserve">ユウシュウシャ </t>
+    </rPh>
+    <rPh sb="46" eb="47">
+      <t xml:space="preserve">ショウ </t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1567,157 +1568,157 @@
   <sheetData>
     <row r="1" spans="1:1" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1744,10 +1745,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -1756,13 +1757,13 @@
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>343</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
@@ -1798,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -1816,13 +1817,13 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="J1" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>8</v>
@@ -1860,34 +1861,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>8</v>
@@ -1923,10 +1924,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>4</v>
@@ -1935,10 +1936,10 @@
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>355</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>8</v>
@@ -1952,17 +1953,17 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E2" t="s">
         <v>358</v>
-      </c>
-      <c r="E2" t="s">
-        <v>359</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1976,10 +1977,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>361</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" t="s">
@@ -2000,17 +2001,17 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" t="s">
+        <v>362</v>
+      </c>
+      <c r="E4" t="s">
         <v>363</v>
-      </c>
-      <c r="E4" t="s">
-        <v>364</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2024,17 +2025,17 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>366</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" t="s">
+        <v>366</v>
+      </c>
+      <c r="E5" t="s">
         <v>367</v>
-      </c>
-      <c r="E5" t="s">
-        <v>368</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2070,37 +2071,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>8</v>
@@ -2114,38 +2115,38 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" t="s">
         <v>81</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>82</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>83</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>84</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>85</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>86</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>87</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>88</v>
-      </c>
-      <c r="L2" t="s">
-        <v>89</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -2159,38 +2160,38 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" t="s">
         <v>92</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>93</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>94</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>95</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>96</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>97</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>98</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>99</v>
-      </c>
-      <c r="L3" t="s">
-        <v>100</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -2204,40 +2205,40 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" t="s">
         <v>102</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" t="s">
         <v>103</v>
       </c>
-      <c r="E4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>104</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>105</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>106</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>107</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>108</v>
       </c>
-      <c r="K4" t="s">
-        <v>109</v>
-      </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M4">
         <v>2</v>
@@ -2273,34 +2274,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>8</v>
@@ -2314,31 +2315,31 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" t="s">
         <v>112</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>113</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>114</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>115</v>
       </c>
-      <c r="G2" t="s">
-        <v>116</v>
-      </c>
       <c r="J2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" t="s">
         <v>87</v>
-      </c>
-      <c r="K2" t="s">
-        <v>88</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2374,46 +2375,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>77</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>8</v>
@@ -2427,49 +2428,49 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" t="s">
         <v>125</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>126</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>127</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>128</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>129</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>130</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>105</v>
+      </c>
+      <c r="K2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" t="s">
         <v>131</v>
       </c>
-      <c r="J2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N2" t="s">
         <v>107</v>
       </c>
-      <c r="L2" t="s">
-        <v>132</v>
-      </c>
-      <c r="M2" t="s">
-        <v>133</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>108</v>
-      </c>
-      <c r="O2" t="s">
-        <v>109</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -2483,34 +2484,34 @@
     </row>
     <row r="3" spans="1:18">
       <c r="A3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="E3" t="s">
         <v>136</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>137</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>138</v>
       </c>
-      <c r="I3" t="s">
-        <v>139</v>
-      </c>
       <c r="J3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K3" t="s">
         <v>85</v>
       </c>
-      <c r="K3" t="s">
+      <c r="N3" t="s">
         <v>86</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>87</v>
-      </c>
-      <c r="O3" t="s">
-        <v>88</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -2701,16 +2702,16 @@
         <v>44131</v>
       </c>
       <c r="C6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" t="s">
+        <v>372</v>
+      </c>
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>35</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2724,22 +2725,22 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B7" s="6">
         <v>46271</v>
       </c>
       <c r="C7" t="s">
+        <v>373</v>
+      </c>
+      <c r="D7" t="s">
         <v>369</v>
       </c>
-      <c r="D7" t="s">
-        <v>371</v>
-      </c>
       <c r="E7" t="s">
+        <v>368</v>
+      </c>
+      <c r="F7" t="s">
         <v>370</v>
-      </c>
-      <c r="F7" t="s">
-        <v>372</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2779,16 +2780,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -2797,16 +2798,16 @@
         <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>6</v>
@@ -2826,25 +2827,25 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>147</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>148</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>149</v>
-      </c>
-      <c r="G2" t="s">
-        <v>150</v>
       </c>
       <c r="H2">
         <v>14400000</v>
@@ -2900,61 +2901,61 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>163</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>8</v>
@@ -2968,37 +2969,37 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" t="s">
         <v>166</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>167</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>168</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>169</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>170</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>171</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>172</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>173</v>
-      </c>
-      <c r="K2" t="s">
-        <v>174</v>
       </c>
       <c r="L2" t="b">
         <v>0</v>
@@ -3022,10 +3023,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="s">
+        <v>174</v>
+      </c>
+      <c r="T2" t="s">
         <v>175</v>
-      </c>
-      <c r="T2" t="s">
-        <v>176</v>
       </c>
       <c r="U2">
         <v>0</v>
@@ -3039,37 +3040,37 @@
     </row>
     <row r="3" spans="1:23">
       <c r="A3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3" t="s">
         <v>178</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>179</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>180</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>181</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>182</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>183</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>172</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="J3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>185</v>
       </c>
       <c r="L3" t="b">
         <v>0</v>
@@ -3093,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -3107,37 +3108,37 @@
     </row>
     <row r="4" spans="1:23">
       <c r="A4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" t="s">
         <v>188</v>
       </c>
-      <c r="D4" t="s">
-        <v>179</v>
-      </c>
-      <c r="E4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>189</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>190</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>191</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
+        <v>172</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="J4" t="s">
-        <v>173</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="L4" t="b">
         <v>0</v>
@@ -3161,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -3175,32 +3176,32 @@
     </row>
     <row r="5" spans="1:23">
       <c r="A5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>194</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>195</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" t="s">
         <v>196</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>197</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>198</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>199</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>200</v>
       </c>
-      <c r="I5" t="s">
-        <v>201</v>
-      </c>
       <c r="J5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -3224,7 +3225,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U5">
         <v>0</v>
@@ -3238,37 +3239,37 @@
     </row>
     <row r="6" spans="1:23">
       <c r="A6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F6" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>203</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>204</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>205</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
+        <v>172</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="J6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -3292,7 +3293,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -3306,37 +3307,37 @@
     </row>
     <row r="7" spans="1:23">
       <c r="A7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" t="s">
+        <v>178</v>
+      </c>
+      <c r="E7" t="s">
+        <v>179</v>
+      </c>
+      <c r="F7" t="s">
         <v>208</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E7" t="s">
-        <v>180</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>209</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>210</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>211</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>212</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" s="5" t="s">
         <v>213</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>214</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -3360,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U7">
         <v>0</v>
@@ -3374,37 +3375,37 @@
     </row>
     <row r="8" spans="1:23">
       <c r="A8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E8" t="s">
+        <v>179</v>
+      </c>
+      <c r="F8" t="s">
         <v>217</v>
       </c>
-      <c r="D8" t="s">
-        <v>179</v>
-      </c>
-      <c r="E8" t="s">
-        <v>180</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>218</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>219</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>220</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
+        <v>212</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="J8" t="s">
-        <v>213</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="L8" t="b">
         <v>0</v>
@@ -3428,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U8">
         <v>0</v>
@@ -3442,37 +3443,37 @@
     </row>
     <row r="9" spans="1:23">
       <c r="A9" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F9" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" t="s">
         <v>223</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="D9" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" t="s">
-        <v>180</v>
-      </c>
-      <c r="F9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G9" t="s">
-        <v>219</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>224</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
+        <v>212</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>225</v>
-      </c>
-      <c r="J9" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="L9" t="b">
         <v>0</v>
@@ -3496,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U9">
         <v>0</v>
@@ -3510,37 +3511,37 @@
     </row>
     <row r="10" spans="1:23">
       <c r="A10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>228</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>229</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>230</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>231</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>232</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
+        <v>172</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="J10" t="s">
-        <v>173</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="L10" t="b">
         <v>0</v>
@@ -3564,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -3601,37 +3602,37 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="D1" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>8</v>
@@ -3645,32 +3646,32 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E2" t="s">
         <v>243</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>244</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" t="s">
         <v>245</v>
       </c>
-      <c r="G2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I2" t="s">
-        <v>246</v>
-      </c>
       <c r="J2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -3684,32 +3685,32 @@
     </row>
     <row r="3" spans="1:15">
       <c r="A3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" t="s">
         <v>249</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>250</v>
       </c>
-      <c r="F3" t="s">
-        <v>251</v>
-      </c>
       <c r="G3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" t="s">
         <v>85</v>
       </c>
-      <c r="H3" t="s">
-        <v>86</v>
-      </c>
       <c r="I3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -3723,32 +3724,32 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>253</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E4" t="s">
         <v>254</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" t="s">
         <v>255</v>
       </c>
-      <c r="F4" t="s">
-        <v>251</v>
-      </c>
-      <c r="G4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" t="s">
-        <v>256</v>
-      </c>
       <c r="J4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -3762,32 +3763,32 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E5" t="s">
         <v>258</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>259</v>
       </c>
-      <c r="F5" t="s">
-        <v>260</v>
-      </c>
       <c r="G5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" t="s">
         <v>85</v>
       </c>
-      <c r="H5" t="s">
-        <v>86</v>
-      </c>
       <c r="I5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -3801,40 +3802,40 @@
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" t="s">
         <v>261</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>262</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>263</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
+        <v>105</v>
+      </c>
+      <c r="H6" t="s">
+        <v>106</v>
+      </c>
+      <c r="I6" t="s">
+        <v>245</v>
+      </c>
+      <c r="J6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K6" t="s">
         <v>264</v>
       </c>
-      <c r="G6" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I6" t="s">
-        <v>246</v>
-      </c>
-      <c r="J6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K6" t="s">
-        <v>265</v>
-      </c>
       <c r="L6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -3873,40 +3874,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" t="s">
+        <v>162</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="L1" t="s">
-        <v>163</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>8</v>
@@ -3920,22 +3921,22 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B2" s="6">
         <v>45211</v>
       </c>
       <c r="C2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E2" t="s">
         <v>274</v>
       </c>
-      <c r="D2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>275</v>
-      </c>
-      <c r="F2" t="s">
-        <v>276</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>
@@ -3944,16 +3945,16 @@
         <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>276</v>
+      </c>
+      <c r="J2" t="s">
         <v>277</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>278</v>
       </c>
-      <c r="K2" t="s">
+      <c r="M2" t="s">
         <v>279</v>
-      </c>
-      <c r="M2" t="s">
-        <v>280</v>
       </c>
       <c r="O2" t="b">
         <v>1</v>
@@ -3964,22 +3965,22 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B3" s="6">
         <v>45577</v>
       </c>
       <c r="C3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3" t="s">
         <v>282</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>283</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>284</v>
-      </c>
-      <c r="F3" t="s">
-        <v>285</v>
       </c>
       <c r="G3" t="s">
         <v>21</v>
@@ -3988,16 +3989,16 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
+        <v>276</v>
+      </c>
+      <c r="J3" t="s">
         <v>277</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>278</v>
       </c>
-      <c r="K3" t="s">
-        <v>279</v>
-      </c>
       <c r="M3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O3" t="b">
         <v>1</v>
@@ -4008,40 +4009,40 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B4" s="6">
         <v>45582</v>
       </c>
       <c r="C4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" t="s">
         <v>288</v>
       </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>288</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>289</v>
       </c>
-      <c r="F4" t="s">
+      <c r="H4" t="s">
         <v>289</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I4" t="s">
         <v>290</v>
       </c>
-      <c r="H4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>291</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
+        <v>278</v>
+      </c>
+      <c r="M4" t="s">
         <v>292</v>
-      </c>
-      <c r="K4" t="s">
-        <v>279</v>
-      </c>
-      <c r="M4" t="s">
-        <v>293</v>
       </c>
       <c r="O4" t="b">
         <v>1</v>
@@ -4052,40 +4053,40 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B5" s="6">
         <v>45840</v>
       </c>
       <c r="C5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E5" t="s">
         <v>295</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>296</v>
+      </c>
+      <c r="G5" t="s">
         <v>295</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>296</v>
       </c>
-      <c r="F5" t="s">
+      <c r="I5" t="s">
+        <v>276</v>
+      </c>
+      <c r="J5" t="s">
+        <v>277</v>
+      </c>
+      <c r="K5" t="s">
+        <v>278</v>
+      </c>
+      <c r="M5" t="s">
         <v>297</v>
-      </c>
-      <c r="G5" t="s">
-        <v>296</v>
-      </c>
-      <c r="H5" t="s">
-        <v>297</v>
-      </c>
-      <c r="I5" t="s">
-        <v>277</v>
-      </c>
-      <c r="J5" t="s">
-        <v>278</v>
-      </c>
-      <c r="K5" t="s">
-        <v>279</v>
-      </c>
-      <c r="M5" t="s">
-        <v>298</v>
       </c>
       <c r="O5" t="b">
         <v>1</v>
@@ -4096,40 +4097,40 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B6" s="6">
         <v>45966</v>
       </c>
       <c r="C6" t="s">
+        <v>299</v>
+      </c>
+      <c r="D6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" t="s">
         <v>300</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>300</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>301</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>301</v>
       </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>302</v>
       </c>
-      <c r="H6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>303</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
+        <v>278</v>
+      </c>
+      <c r="M6" t="s">
         <v>304</v>
-      </c>
-      <c r="K6" t="s">
-        <v>279</v>
-      </c>
-      <c r="M6" t="s">
-        <v>305</v>
       </c>
       <c r="O6" t="b">
         <v>1</v>
@@ -4140,40 +4141,40 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B7" s="6">
         <v>45903</v>
       </c>
       <c r="C7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" t="s">
         <v>307</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>307</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
         <v>308</v>
       </c>
-      <c r="F7" t="s">
+      <c r="H7" t="s">
         <v>308</v>
       </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>309</v>
       </c>
-      <c r="H7" t="s">
-        <v>309</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>310</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
+        <v>278</v>
+      </c>
+      <c r="M7" t="s">
         <v>311</v>
-      </c>
-      <c r="K7" t="s">
-        <v>279</v>
-      </c>
-      <c r="M7" t="s">
-        <v>312</v>
       </c>
       <c r="O7" t="b">
         <v>1</v>
@@ -4184,40 +4185,40 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B8" s="6">
         <v>46051</v>
       </c>
       <c r="C8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" t="s">
+        <v>294</v>
+      </c>
+      <c r="E8" t="s">
         <v>314</v>
       </c>
-      <c r="D8" t="s">
-        <v>295</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>315</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>316</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>317</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
+        <v>276</v>
+      </c>
+      <c r="J8" t="s">
+        <v>277</v>
+      </c>
+      <c r="K8" t="s">
+        <v>278</v>
+      </c>
+      <c r="M8" t="s">
         <v>318</v>
-      </c>
-      <c r="I8" t="s">
-        <v>277</v>
-      </c>
-      <c r="J8" t="s">
-        <v>278</v>
-      </c>
-      <c r="K8" t="s">
-        <v>279</v>
-      </c>
-      <c r="M8" t="s">
-        <v>319</v>
       </c>
       <c r="O8" t="b">
         <v>1</v>
@@ -4228,37 +4229,37 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B9" s="6">
         <v>46035</v>
       </c>
       <c r="C9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" t="s">
         <v>321</v>
       </c>
-      <c r="D9" t="s">
-        <v>295</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>322</v>
       </c>
-      <c r="F9" t="s">
-        <v>323</v>
-      </c>
       <c r="G9" t="s">
+        <v>321</v>
+      </c>
+      <c r="H9" t="s">
         <v>322</v>
       </c>
-      <c r="H9" t="s">
-        <v>323</v>
-      </c>
       <c r="I9" t="s">
+        <v>276</v>
+      </c>
+      <c r="J9" t="s">
         <v>277</v>
       </c>
-      <c r="J9" t="s">
-        <v>278</v>
-      </c>
       <c r="K9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -4269,37 +4270,37 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B10" s="6">
         <v>46070</v>
       </c>
       <c r="C10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E10" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" t="s">
         <v>325</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
+        <v>324</v>
+      </c>
+      <c r="H10" t="s">
+        <v>325</v>
+      </c>
+      <c r="I10" t="s">
         <v>326</v>
       </c>
-      <c r="G10" t="s">
-        <v>325</v>
-      </c>
-      <c r="H10" t="s">
-        <v>326</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>327</v>
       </c>
-      <c r="J10" t="s">
-        <v>328</v>
-      </c>
       <c r="K10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O10" t="b">
         <v>1</v>
@@ -4310,37 +4311,37 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B11" s="6">
         <v>45279</v>
       </c>
       <c r="C11" t="s">
+        <v>329</v>
+      </c>
+      <c r="D11" t="s">
+        <v>329</v>
+      </c>
+      <c r="E11" t="s">
         <v>330</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>330</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
+        <v>330</v>
+      </c>
+      <c r="H11" t="s">
+        <v>330</v>
+      </c>
+      <c r="I11" t="s">
         <v>331</v>
       </c>
-      <c r="F11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G11" t="s">
-        <v>331</v>
-      </c>
-      <c r="H11" t="s">
-        <v>331</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="J11" t="s">
         <v>332</v>
       </c>
-      <c r="J11" t="s">
-        <v>333</v>
-      </c>
       <c r="K11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O11" t="b">
         <v>1</v>
@@ -4351,37 +4352,37 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B12" s="6">
         <v>46141</v>
       </c>
       <c r="C12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D12" t="s">
+        <v>334</v>
+      </c>
+      <c r="E12" t="s">
         <v>335</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>335</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
+        <v>335</v>
+      </c>
+      <c r="H12" t="s">
+        <v>335</v>
+      </c>
+      <c r="I12" t="s">
         <v>336</v>
       </c>
-      <c r="F12" t="s">
-        <v>336</v>
-      </c>
-      <c r="G12" t="s">
-        <v>336</v>
-      </c>
-      <c r="H12" t="s">
-        <v>336</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>337</v>
       </c>
-      <c r="J12" t="s">
-        <v>338</v>
-      </c>
       <c r="K12" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="O12" t="b">
         <v>1</v>
